--- a/output/stock_quant_scores/AMZN_info.xlsx
+++ b/output/stock_quant_scores/AMZN_info.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FP2"/>
+  <dimension ref="A1:FT2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1066,220 +1066,240 @@
       </c>
       <c r="DY1" s="1" t="inlineStr">
         <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DZ1" s="1" t="inlineStr">
+        <is>
           <t>longName</t>
         </is>
       </c>
-      <c r="DZ1" s="1" t="inlineStr">
+      <c r="EA1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketTime</t>
+        </is>
+      </c>
+      <c r="EB1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="EC1" s="1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="ED1" s="1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="EE1" s="1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="EF1" s="1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="EG1" s="1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="EH1" s="1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="EI1" s="1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="EJ1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="EK1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="EL1" s="1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="EM1" s="1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EN1" s="1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampStart</t>
+        </is>
+      </c>
+      <c r="EO1" s="1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EP1" s="1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="EQ1" s="1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="ER1" s="1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="ES1" s="1" t="inlineStr">
+        <is>
+          <t>epsCurrentYear</t>
+        </is>
+      </c>
+      <c r="ET1" s="1" t="inlineStr">
+        <is>
+          <t>priceEpsCurrentYear</t>
+        </is>
+      </c>
+      <c r="EU1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EV1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EW1" s="1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EX1" s="1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EY1" s="1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EZ1" s="1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="FA1" s="1" t="inlineStr">
+        <is>
+          <t>averageAnalystRating</t>
+        </is>
+      </c>
+      <c r="FB1" s="1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="FC1" s="1" t="inlineStr">
         <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="EA1" s="1" t="inlineStr">
+      <c r="FD1" s="1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
-      <c r="EB1" s="1" t="inlineStr">
+      <c r="FE1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="FF1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketPrice</t>
+        </is>
+      </c>
+      <c r="FG1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketChange</t>
+        </is>
+      </c>
+      <c r="FH1" s="1" t="inlineStr">
         <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="EC1" s="1" t="inlineStr">
+      <c r="FI1" s="1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="ED1" s="1" t="inlineStr">
+      <c r="FJ1" s="1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="EE1" s="1" t="inlineStr">
+      <c r="FK1" s="1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="EF1" s="1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EG1" s="1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EH1" s="1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EI1" s="1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EJ1" s="1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EK1" s="1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EL1" s="1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="EM1" s="1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EN1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EO1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EP1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="EQ1" s="1" t="inlineStr">
+      <c r="FL1" s="1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="ER1" s="1" t="inlineStr">
+      <c r="FM1" s="1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="ES1" s="1" t="inlineStr">
+      <c r="FN1" s="1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="ET1" s="1" t="inlineStr">
+      <c r="FO1" s="1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="EU1" s="1" t="inlineStr">
+      <c r="FP1" s="1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="EV1" s="1" t="inlineStr">
+      <c r="FQ1" s="1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="EW1" s="1" t="inlineStr">
+      <c r="FR1" s="1" t="inlineStr">
         <is>
           <t>earningsTimestamp</t>
         </is>
       </c>
-      <c r="EX1" s="1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EY1" s="1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EZ1" s="1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampStart</t>
-        </is>
-      </c>
-      <c r="FA1" s="1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampEnd</t>
-        </is>
-      </c>
-      <c r="FB1" s="1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="FC1" s="1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="FD1" s="1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="FE1" s="1" t="inlineStr">
-        <is>
-          <t>epsCurrentYear</t>
-        </is>
-      </c>
-      <c r="FF1" s="1" t="inlineStr">
-        <is>
-          <t>priceEpsCurrentYear</t>
-        </is>
-      </c>
-      <c r="FG1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="FH1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="FI1" s="1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="FJ1" s="1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="FK1" s="1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="FL1" s="1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="FM1" s="1" t="inlineStr">
-        <is>
-          <t>averageAnalystRating</t>
-        </is>
-      </c>
-      <c r="FN1" s="1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="FO1" s="1" t="inlineStr">
+      <c r="FS1" s="1" t="inlineStr">
         <is>
           <t>displayName</t>
         </is>
       </c>
-      <c r="FP1" s="1" t="inlineStr">
+      <c r="FT1" s="1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -1364,7 +1384,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Jeffrey P. Bezos', 'age': 60, 'title': 'Founder &amp; Executive Chairman', 'yearBorn': 1964, 'fiscalYear': 2024, 'totalPay': 1681840, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Andrew R. Jassy', 'age': 56, 'title': 'President, CEO &amp; Director', 'yearBorn': 1968, 'fiscalYear': 2024, 'totalPay': 1596889, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Brian T. Olsavsky', 'age': 60, 'title': 'Senior VP &amp; CFO', 'yearBorn': 1964, 'fiscalYear': 2024, 'totalPay': 371900, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. David A. Zapolsky J.D.', 'age': 60, 'title': 'Senior VP, Chief Global Affairs &amp; Legal Officer', 'yearBorn': 1964, 'fiscalYear': 2024, 'totalPay': 371900, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Douglas J. Herrington', 'age': 57, 'title': 'Chief Executive Officer of Worldwide Amazon Stores', 'yearBorn': 1967, 'fiscalYear': 2024, 'totalPay': 386435, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Matthew S. Garman', 'age': 47, 'title': 'Chief Executive Officer of Amazon Web Series', 'yearBorn': 1977, 'fiscalYear': 2024, 'totalPay': 384275, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Shelley L. Reynolds', 'age': 59, 'title': 'VP, Worldwide Controller &amp; Principal Accounting Officer', 'yearBorn': 1965, 'fiscalYear': 2024, 'totalPay': 163200, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Dr. Werner  Vogels', 'title': 'Chief Technology Officer', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Dave  Fildes', 'title': 'Director of Investor Relations', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Anuradha  Aggarwal', 'title': 'CMO &amp; Director of User Growth', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Jeffrey P. Bezos', 'age': 60, 'title': 'Founder &amp; Executive Chairman', 'yearBorn': 1964, 'fiscalYear': 2024, 'totalPay': 1681840, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Andrew R. Jassy', 'age': 56, 'title': 'President, CEO &amp; Director', 'yearBorn': 1968, 'fiscalYear': 2024, 'totalPay': 1596889, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Brian T. Olsavsky', 'age': 60, 'title': 'Senior VP &amp; CFO', 'yearBorn': 1964, 'fiscalYear': 2024, 'totalPay': 371900, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. David A. Zapolsky J.D.', 'age': 60, 'title': 'Senior VP, Chief Global Affairs &amp; Legal Officer', 'yearBorn': 1964, 'fiscalYear': 2024, 'totalPay': 371900, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Douglas J. Herrington', 'age': 57, 'title': 'Chief Executive Officer of Worldwide Amazon Stores', 'yearBorn': 1967, 'fiscalYear': 2024, 'totalPay': 386435, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Matthew S. Garman', 'age': 47, 'title': 'Chief Executive Officer of Amazon Web Series', 'yearBorn': 1977, 'fiscalYear': 2024, 'totalPay': 384275, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Shelley L. Reynolds', 'age': 59, 'title': 'VP, Worldwide Controller &amp; Principal Accounting Officer', 'yearBorn': 1965, 'fiscalYear': 2024, 'totalPay': 163200, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Dr. Werner  Vogels', 'title': 'Chief Technology Officer', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Dave  Fildes', 'title': 'Vice President of Investor Relations', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Beth  Galetti M.B.A.', 'title': 'Senior Vice President of People eXperience and Technology', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -1405,28 +1425,28 @@
         <v>2</v>
       </c>
       <c r="AC2" t="n">
-        <v>220.71</v>
+        <v>218.15</v>
       </c>
       <c r="AD2" t="n">
-        <v>224.19</v>
+        <v>219</v>
       </c>
       <c r="AE2" t="n">
-        <v>219.54</v>
+        <v>218.02</v>
       </c>
       <c r="AF2" t="n">
-        <v>224.56</v>
+        <v>221.03</v>
       </c>
       <c r="AG2" t="n">
-        <v>220.71</v>
+        <v>218.15</v>
       </c>
       <c r="AH2" t="n">
-        <v>224.19</v>
+        <v>219</v>
       </c>
       <c r="AI2" t="n">
-        <v>219.54</v>
+        <v>218.02</v>
       </c>
       <c r="AJ2" t="n">
-        <v>224.56</v>
+        <v>221.03</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
@@ -1435,40 +1455,40 @@
         <v>1.309</v>
       </c>
       <c r="AM2" t="n">
-        <v>33.587654</v>
+        <v>33.554195</v>
       </c>
       <c r="AN2" t="n">
-        <v>35.826828</v>
+        <v>35.736584</v>
       </c>
       <c r="AO2" t="n">
-        <v>33707654</v>
+        <v>39538465</v>
       </c>
       <c r="AP2" t="n">
-        <v>33707653</v>
+        <v>39542108</v>
       </c>
       <c r="AQ2" t="n">
-        <v>43221309</v>
+        <v>42300922</v>
       </c>
       <c r="AR2" t="n">
-        <v>50376450</v>
+        <v>51034420</v>
       </c>
       <c r="AS2" t="n">
-        <v>50376450</v>
+        <v>51034420</v>
       </c>
       <c r="AT2" t="n">
-        <v>220.15</v>
+        <v>219.67</v>
       </c>
       <c r="AU2" t="n">
-        <v>220.34</v>
+        <v>219.92</v>
       </c>
       <c r="AV2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AW2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AX2" t="n">
-        <v>2349853310976</v>
+        <v>2343934361600</v>
       </c>
       <c r="AY2" t="n">
         <v>161.38</v>
@@ -1483,13 +1503,13 @@
         <v>0.065625</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.5070446</v>
+        <v>3.498211</v>
       </c>
       <c r="BD2" t="n">
-        <v>227.6894</v>
+        <v>227.3838</v>
       </c>
       <c r="BE2" t="n">
-        <v>214.78935</v>
+        <v>214.75134</v>
       </c>
       <c r="BF2" t="n">
         <v>0</v>
@@ -1506,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>2420242644992</v>
+        <v>2410324426752</v>
       </c>
       <c r="BK2" t="n">
         <v>0.105399996</v>
@@ -1518,31 +1538,31 @@
         <v>10664912097</v>
       </c>
       <c r="BN2" t="n">
-        <v>68648147</v>
+        <v>69908794</v>
       </c>
       <c r="BO2" t="n">
-        <v>63646074</v>
+        <v>75684758</v>
       </c>
       <c r="BP2" t="n">
-        <v>1753920000</v>
+        <v>1755216000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1756425600</v>
+        <v>1757894400</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.0064</v>
+        <v>0.0066000004</v>
       </c>
       <c r="BS2" t="n">
         <v>0.08445</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.66312</v>
+        <v>0.66321</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.57</v>
+        <v>2.02</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.0070999996</v>
+        <v>0.0073</v>
       </c>
       <c r="BW2" t="n">
         <v>10664912097</v>
@@ -1551,7 +1571,7 @@
         <v>31.311</v>
       </c>
       <c r="BY2" t="n">
-        <v>7.036984</v>
+        <v>7.019258</v>
       </c>
       <c r="BZ2" t="n">
         <v>1735603200</v>
@@ -1569,7 +1589,7 @@
         <v>70623002624</v>
       </c>
       <c r="CE2" t="n">
-        <v>6.56</v>
+        <v>6.55</v>
       </c>
       <c r="CF2" t="n">
         <v>6.15</v>
@@ -1583,16 +1603,16 @@
         <v>1654473600</v>
       </c>
       <c r="CI2" t="n">
-        <v>3.612</v>
+        <v>3.597</v>
       </c>
       <c r="CJ2" t="n">
-        <v>18.084</v>
+        <v>18.01</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.14636683</v>
+        <v>0.17952025</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.16333759</v>
+        <v>0.1529237</v>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
@@ -1600,7 +1620,7 @@
         </is>
       </c>
       <c r="CN2" t="n">
-        <v>220.335</v>
+        <v>219.78</v>
       </c>
       <c r="CO2" t="n">
         <v>306</v>
@@ -1615,7 +1635,7 @@
         <v>265</v>
       </c>
       <c r="CS2" t="n">
-        <v>1.33333</v>
+        <v>1.30303</v>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
@@ -1722,7 +1742,7 @@
       </c>
       <c r="DW2" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="DX2" t="inlineStr">
@@ -1732,159 +1752,171 @@
       </c>
       <c r="DY2" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
           <t>Amazon.com, Inc.</t>
         </is>
       </c>
-      <c r="DZ2" t="b">
+      <c r="EA2" t="n">
+        <v>1758931197</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>1758916801</v>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>NMS</t>
+        </is>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>finmb_18749</t>
+        </is>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>America/New_York</t>
+        </is>
+      </c>
+      <c r="EF2" t="inlineStr">
+        <is>
+          <t>EDT</t>
+        </is>
+      </c>
+      <c r="EG2" t="n">
+        <v>-14400000</v>
+      </c>
+      <c r="EH2" t="inlineStr">
+        <is>
+          <t>us_market</t>
+        </is>
+      </c>
+      <c r="EI2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>0.7471950000000001</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>219.78</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>1761854400</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>1761854400</v>
+      </c>
+      <c r="EN2" t="n">
+        <v>1753995600</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>1753995600</v>
+      </c>
+      <c r="EP2" t="b">
         <v>1</v>
       </c>
-      <c r="EA2" t="n">
+      <c r="EQ2" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="ES2" t="n">
+        <v>6.65027</v>
+      </c>
+      <c r="ET2" t="n">
+        <v>33.048283</v>
+      </c>
+      <c r="EU2" t="n">
+        <v>-7.6038055</v>
+      </c>
+      <c r="EV2" t="n">
+        <v>-0.0334404</v>
+      </c>
+      <c r="EW2" t="n">
+        <v>5.028656</v>
+      </c>
+      <c r="EX2" t="n">
+        <v>0.02341618</v>
+      </c>
+      <c r="EY2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA2" t="inlineStr">
+        <is>
+          <t>1.3 - Strong Buy</t>
+        </is>
+      </c>
+      <c r="FB2" t="b">
+        <v>0</v>
+      </c>
+      <c r="FC2" t="b">
+        <v>1</v>
+      </c>
+      <c r="FD2" t="n">
         <v>863703000000</v>
       </c>
-      <c r="EB2" t="n">
-        <v>-0.375</v>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>219.54 - 224.56</t>
-        </is>
-      </c>
-      <c r="ED2" t="inlineStr">
+      <c r="FE2" t="n">
+        <v>0.22591034</v>
+      </c>
+      <c r="FF2" t="n">
+        <v>220.2765</v>
+      </c>
+      <c r="FG2" t="n">
+        <v>0.49650574</v>
+      </c>
+      <c r="FH2" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="FI2" t="inlineStr">
+        <is>
+          <t>218.02 - 221.03</t>
+        </is>
+      </c>
+      <c r="FJ2" t="inlineStr">
         <is>
           <t>NasdaqGS</t>
         </is>
       </c>
-      <c r="EE2" t="n">
-        <v>43221309</v>
-      </c>
-      <c r="EF2" t="inlineStr">
-        <is>
-          <t>NMS</t>
-        </is>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>finmb_18749</t>
-        </is>
-      </c>
-      <c r="EH2" t="inlineStr">
-        <is>
-          <t>America/New_York</t>
-        </is>
-      </c>
-      <c r="EI2" t="inlineStr">
-        <is>
-          <t>EDT</t>
-        </is>
-      </c>
-      <c r="EJ2" t="n">
-        <v>-14400000</v>
-      </c>
-      <c r="EK2" t="inlineStr">
-        <is>
-          <t>us_market</t>
-        </is>
-      </c>
-      <c r="EL2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EM2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="EN2" t="n">
-        <v>1758740008</v>
-      </c>
-      <c r="EO2" t="n">
-        <v>-0.16990621</v>
-      </c>
-      <c r="EP2" t="n">
-        <v>220.335</v>
-      </c>
-      <c r="EQ2" t="n">
-        <v>58.955</v>
-      </c>
-      <c r="ER2" t="n">
-        <v>0.36531788</v>
-      </c>
-      <c r="ES2" t="inlineStr">
+      <c r="FK2" t="n">
+        <v>42300922</v>
+      </c>
+      <c r="FL2" t="n">
+        <v>58.399994</v>
+      </c>
+      <c r="FM2" t="n">
+        <v>0.36187875</v>
+      </c>
+      <c r="FN2" t="inlineStr">
         <is>
           <t>161.38 - 242.52</t>
         </is>
       </c>
-      <c r="ET2" t="n">
-        <v>-22.184998</v>
-      </c>
-      <c r="EU2" t="n">
-        <v>-0.09147698</v>
-      </c>
-      <c r="EV2" t="n">
-        <v>14.636683</v>
-      </c>
-      <c r="EW2" t="n">
+      <c r="FO2" t="n">
+        <v>-22.740005</v>
+      </c>
+      <c r="FP2" t="n">
+        <v>-0.09376548</v>
+      </c>
+      <c r="FQ2" t="n">
+        <v>17.952024</v>
+      </c>
+      <c r="FR2" t="n">
         <v>1753992000</v>
       </c>
-      <c r="EX2" t="n">
-        <v>1761854400</v>
-      </c>
-      <c r="EY2" t="n">
-        <v>1761854400</v>
-      </c>
-      <c r="EZ2" t="n">
-        <v>1753995600</v>
-      </c>
-      <c r="FA2" t="n">
-        <v>1753995600</v>
-      </c>
-      <c r="FB2" t="b">
-        <v>1</v>
-      </c>
-      <c r="FC2" t="n">
-        <v>6.56</v>
-      </c>
-      <c r="FD2" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="FE2" t="n">
-        <v>6.65027</v>
-      </c>
-      <c r="FF2" t="n">
-        <v>33.131737</v>
-      </c>
-      <c r="FG2" t="n">
-        <v>-7.3544006</v>
-      </c>
-      <c r="FH2" t="n">
-        <v>-0.032300144</v>
-      </c>
-      <c r="FI2" t="n">
-        <v>5.5456543</v>
-      </c>
-      <c r="FJ2" t="n">
-        <v>0.025819037</v>
-      </c>
-      <c r="FK2" t="n">
-        <v>15</v>
-      </c>
-      <c r="FL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="FM2" t="inlineStr">
-        <is>
-          <t>1.3 - Strong Buy</t>
-        </is>
-      </c>
-      <c r="FN2" t="b">
-        <v>0</v>
-      </c>
-      <c r="FO2" t="inlineStr">
+      <c r="FS2" t="inlineStr">
         <is>
           <t>Amazon.com</t>
         </is>
       </c>
-      <c r="FP2" t="n">
-        <v>1.9565</v>
+      <c r="FT2" t="n">
+        <v>1.9482</v>
       </c>
     </row>
   </sheetData>
